--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484358_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484358_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8095</v>
+        <v>4.2689</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6044</v>
+        <v>3.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2051</v>
+        <v>1.0689</v>
       </c>
       <c r="G2" t="n">
         <v>3.5019</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0027</v>
+        <v>-0.5379</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.03</v>
+        <v>-0.4345</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0328</v>
+        <v>-0.1034</v>
       </c>
       <c r="V2" t="n">
         <v>0.1328</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1305</v>
+        <v>3.9163</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9349</v>
+        <v>5.2382</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8044</v>
+        <v>-1.3219</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8869</v>
@@ -688,13 +688,13 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1309</v>
+        <v>-0.0833</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8335</v>
+        <v>-0.5302</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9644</v>
+        <v>0.4469</v>
       </c>
       <c r="V3" t="n">
         <v>3.3238</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.8948</v>
       </c>
       <c r="E4" t="n">
         <v>0.7265</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0224</v>
+        <v>0.1683</v>
       </c>
       <c r="G4" t="n">
         <v>2.6439</v>
@@ -766,13 +766,13 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2403</v>
+        <v>-1.0497</v>
       </c>
       <c r="T4" t="n">
         <v>-0.7179</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5224</v>
+        <v>-0.3317</v>
       </c>
       <c r="V4" t="n">
         <v>0.2772</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2474</v>
+        <v>0.3757</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3067</v>
+        <v>1.4079</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0594</v>
+        <v>-1.0322</v>
       </c>
       <c r="G5" t="n">
         <v>3.1592</v>
@@ -844,13 +844,13 @@
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2047</v>
+        <v>-0.0764</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2888</v>
+        <v>-0.1877</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.1113</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7537</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0219</v>
+        <v>0.0053</v>
       </c>
       <c r="E6" t="n">
         <v>-0.0401</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="G6" t="n">
         <v>0.2901</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.312</v>
+        <v>-0.2848</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0605</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2515</v>
+        <v>-0.2242</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.247</v>
+        <v>-1.006</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0201</v>
+        <v>-1.6156</v>
       </c>
       <c r="F7" t="n">
-        <v>0.773</v>
+        <v>0.6096</v>
       </c>
       <c r="G7" t="n">
         <v>1.941</v>
@@ -1000,13 +1000,13 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7033</v>
+        <v>-0.4623</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.3823</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0835</v>
+        <v>-0.0799</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5313</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6521</v>
+        <v>-2.1305</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9388</v>
+        <v>-1.4444</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7133</v>
+        <v>-0.6861</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3484</v>
@@ -1078,13 +1078,13 @@
         <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4694</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3936</v>
+        <v>-0.112</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="V8" t="n">
         <v>-1.7731</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.919</v>
+        <v>-4.6694</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.9318</v>
+        <v>-2.5996</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0128</v>
+        <v>-2.0697</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.5693</v>
+        <v>-4.1593</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3735</v>
+        <v>-1.2471</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.1958</v>
+        <v>-2.9122</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.2894</v>
+        <v>-2.251</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6335</v>
+        <v>-0.9581</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.6559</v>
+        <v>-1.2929</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2799</v>
+        <v>-1.9083</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2599</v>
+        <v>-0.2891</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5399</v>
+        <v>-1.6192</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6741</v>
+        <v>-0.401</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6657</v>
+        <v>-0.3486</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0083</v>
+        <v>-0.0524</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5198</v>
+        <v>-1.0858</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5198</v>
+        <v>-1.0858</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2451</v>
+        <v>-4.919</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.903</v>
+        <v>-5.9318</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3421</v>
+        <v>1.0128</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.1593</v>
+        <v>-4.5693</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2471</v>
+        <v>-1.3735</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9122</v>
+        <v>-3.1958</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.251</v>
+        <v>-4.2894</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9581</v>
+        <v>-1.6335</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2929</v>
+        <v>-2.6559</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9083</v>
+        <v>-0.2799</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2891</v>
+        <v>0.2599</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6192</v>
+        <v>-0.5399</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9767</v>
+        <v>-0.6741</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.652</v>
+        <v>-0.6657</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3247</v>
+        <v>-0.0083</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0858</v>
+        <v>0.5198</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0858</v>
+        <v>0.5198</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5277</v>
+        <v>-6.4575</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1133</v>
+        <v>-3.3155</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4144</v>
+        <v>-3.1421</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2483</v>
@@ -1312,13 +1312,13 @@
         <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2793</v>
+        <v>-1.2092</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1127</v>
+        <v>-0.3149</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1666</v>
+        <v>-0.8943</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4373</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.721300000000001</v>
+        <v>-9.721399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.374599999999998</v>
+        <v>-4.374400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.3469</v>
+        <v>-5.347000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>0.3238999999999987</v>
@@ -1390,13 +1390,13 @@
         <v>12.6972</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.7874</v>
+        <v>-4.7877</v>
       </c>
       <c r="T12" t="n">
         <v>-3.7543</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0329</v>
+        <v>-1.033</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3276</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5265</v>
+        <v>3.7263</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5691</v>
+        <v>2.0413</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9574</v>
+        <v>1.685</v>
       </c>
       <c r="G13" t="n">
         <v>0.371</v>
@@ -1468,13 +1468,13 @@
         <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>4.8122</v>
+        <v>2.012</v>
       </c>
       <c r="T13" t="n">
-        <v>3.7503</v>
+        <v>1.2225</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0619</v>
+        <v>0.7895</v>
       </c>
       <c r="V13" t="n">
         <v>3.1014</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6998</v>
+        <v>2.8091</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6413</v>
+        <v>2.9932</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0585</v>
+        <v>-0.1842</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2926</v>
+        <v>0.6899</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7861</v>
+        <v>1.0136</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0788</v>
+        <v>-0.3237</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7774</v>
+        <v>2.8026</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5718</v>
+        <v>2.0466</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3492</v>
+        <v>0.756</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4848</v>
+        <v>-2.1127</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2144</v>
+        <v>-1.033</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2704</v>
+        <v>-1.0797</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1885</v>
+        <v>0.3612</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6219</v>
+        <v>0.1906</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5666</v>
+        <v>0.1705</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2075</v>
+        <v>2.0197</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6899</v>
+        <v>1.5959</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4824</v>
+        <v>0.4238</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6899</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0136</v>
+        <v>-0.2599</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3237</v>
+        <v>0.9167</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8026</v>
+        <v>1.4209</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0466</v>
+        <v>0.6382</v>
       </c>
       <c r="L15" t="n">
-        <v>0.756</v>
+        <v>0.7827</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1127</v>
+        <v>-0.7641</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.033</v>
+        <v>-0.8982</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0797</v>
+        <v>0.134</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2404</v>
+        <v>0.7731</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1127</v>
+        <v>0.0428</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1277</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2822</v>
+        <v>1.7183</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5848</v>
+        <v>0.9335</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6975</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.2926</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2599</v>
+        <v>-0.7861</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9167</v>
+        <v>1.0788</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4209</v>
+        <v>0.7774</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6382</v>
+        <v>-0.5718</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7827</v>
+        <v>1.3492</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7641</v>
+        <v>-0.4848</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8982</v>
+        <v>-0.2144</v>
       </c>
       <c r="O16" t="n">
-        <v>0.134</v>
+        <v>-0.2704</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0357</v>
+        <v>0.207</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9684</v>
+        <v>-0.0859</v>
       </c>
       <c r="U16" t="n">
-        <v>1.004</v>
+        <v>0.2929</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3869</v>
+        <v>1.2186</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1089</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. POCULL DURAN</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9313</v>
+        <v>1.6828</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0447</v>
+        <v>0.5525</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8866000000000001</v>
+        <v>1.1302</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1422</v>
+        <v>-0.6194</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1673</v>
+        <v>-0.4996</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3095</v>
+        <v>-0.1198</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2179</v>
+        <v>0.2196</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6319</v>
+        <v>0.4733</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8498</v>
+        <v>-0.2536</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0757</v>
+        <v>-0.839</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4646</v>
+        <v>-0.9729</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5403</v>
+        <v>0.1338</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>2.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1876</v>
+        <v>0.626</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1732</v>
+        <v>0.091</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0144</v>
+        <v>0.535</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8157</v>
+        <v>1.4332</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5021</v>
+        <v>0.8457</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3178</v>
+        <v>0.5875</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7023</v>
+        <v>0.2785</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5273</v>
+        <v>0.0481</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1751</v>
+        <v>0.2304</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7772</v>
+        <v>1.1029</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7368</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>1.0403</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.8245</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2095</v>
+        <v>-0.0146</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1346</v>
+        <v>-0.8099</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1133</v>
+        <v>0.432</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3026</v>
+        <v>0.1102</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4159</v>
+        <v>0.3218</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>L. POCULL DURAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.593</v>
+        <v>1.1478</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4413</v>
+        <v>0.0447</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1517</v>
+        <v>1.1032</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2785</v>
+        <v>0.1422</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0481</v>
+        <v>-0.1673</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2304</v>
+        <v>0.3095</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1029</v>
+        <v>0.2179</v>
       </c>
       <c r="K19" t="n">
-        <v>0.06270000000000001</v>
+        <v>-0.6319</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0403</v>
+        <v>0.8498</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8245</v>
+        <v>-0.0757</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0146</v>
+        <v>0.4646</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8099</v>
+        <v>-0.5403</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4082</v>
+        <v>0.0289</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2943</v>
+        <v>-0.1732</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.114</v>
+        <v>0.2021</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>M. LLUCIÀ MONSÓ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.276</v>
+        <v>0.9362</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2564</v>
+        <v>-0.2999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5324</v>
+        <v>1.2361</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6194</v>
+        <v>0.7023</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4996</v>
+        <v>0.5273</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1198</v>
+        <v>0.1751</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2196</v>
+        <v>0.7772</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4733</v>
+        <v>0.7368</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2536</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.839</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9729</v>
+        <v>-0.2095</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1338</v>
+        <v>0.1346</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9301</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0.2338</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7179</v>
+        <v>-0.1004</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.06279999999999999</v>
+        <v>0.3342</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5223</v>
+        <v>-1.5379</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8935</v>
+        <v>-2.6913</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3712</v>
+        <v>1.1534</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9391</v>
@@ -2092,13 +2092,13 @@
         <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1478</v>
+        <v>1.1322</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0167</v>
+        <v>0.2189</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1311</v>
+        <v>0.9133</v>
       </c>
       <c r="V21" t="n">
         <v>0.2224</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0884</v>
+        <v>-3.54</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9721</v>
+        <v>-0.6687</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1164</v>
+        <v>-2.8712</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8987</v>
@@ -2170,13 +2170,13 @@
         <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.893</v>
+        <v>-0.3446</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.4835</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1062</v>
+        <v>0.1389</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8828</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.721300000000001</v>
+        <v>10.3955</v>
       </c>
       <c r="E23" t="n">
-        <v>5.346999999999999</v>
+        <v>5.346899999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>4.3743</v>
+        <v>5.0486</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3239000000000001</v>
@@ -2218,10 +2218,10 @@
         <v>-2.347</v>
       </c>
       <c r="I23" t="n">
-        <v>2.023400000000001</v>
+        <v>2.0234</v>
       </c>
       <c r="J23" t="n">
-        <v>9.641399999999999</v>
+        <v>9.641400000000001</v>
       </c>
       <c r="K23" t="n">
         <v>2.890600000000001</v>
@@ -2233,7 +2233,7 @@
         <v>-9.965299999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.237900000000001</v>
+        <v>-5.2379</v>
       </c>
       <c r="O23" t="n">
         <v>-4.7275</v>
@@ -2248,19 +2248,19 @@
         <v>15.6273</v>
       </c>
       <c r="S23" t="n">
-        <v>4.7876</v>
+        <v>5.4616</v>
       </c>
       <c r="T23" t="n">
         <v>1.033</v>
       </c>
       <c r="U23" t="n">
-        <v>3.7544</v>
+        <v>4.4285</v>
       </c>
       <c r="V23" t="n">
-        <v>2.327600000000001</v>
+        <v>2.3276</v>
       </c>
       <c r="W23" t="n">
-        <v>7.3696</v>
+        <v>7.369599999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-5.0421</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484358_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484358_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.1328</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-1.0309</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>À. ANTEQUERA SOLER</t>
+          <t>A. ANTEQUERA SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.1328</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0858</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.5198</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-7.3696</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1416,7 +1472,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1484,6 +1540,11 @@
       </c>
       <c r="X13" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1494,7 +1555,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1562,84 +1623,94 @@
       </c>
       <c r="X14" t="n">
         <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0197</v>
+        <v>1.8349</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5959</v>
+        <v>1.8349</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4238</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6568000000000001</v>
+        <v>1.8349</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2599</v>
+        <v>1.2279</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9167</v>
+        <v>0.607</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4209</v>
+        <v>1.8349</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6382</v>
+        <v>1.2279</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7827</v>
+        <v>0.607</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7641</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8982</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7731</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0428</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7302999999999999</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1650,7 +1721,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1718,6 +1789,11 @@
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1728,7 +1804,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1796,6 +1872,11 @@
       </c>
       <c r="X17" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1806,7 +1887,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1874,153 +1955,163 @@
       </c>
       <c r="X18" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. POCULL DURAN</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1478</v>
+        <v>1.4057</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0447</v>
+        <v>0.9819</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1032</v>
+        <v>0.4238</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1422</v>
+        <v>0.0428</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1673</v>
+        <v>-0.8739</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3095</v>
+        <v>0.9167</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2179</v>
+        <v>0.8069</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6319</v>
+        <v>0.0243</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8498</v>
+        <v>0.7827</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0757</v>
+        <v>-0.7641</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4646</v>
+        <v>-0.8982</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5403</v>
+        <v>0.134</v>
       </c>
       <c r="P19" t="n">
         <v>0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0289</v>
+        <v>0.7731</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1732</v>
+        <v>0.0428</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2021</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>L. POCULL DURAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9362</v>
+        <v>1.1478</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2999</v>
+        <v>0.0447</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2361</v>
+        <v>1.1032</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7023</v>
+        <v>0.1422</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5273</v>
+        <v>-0.1673</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1751</v>
+        <v>0.3095</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7772</v>
+        <v>0.2179</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7368</v>
+        <v>-0.6319</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>0.8498</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.0757</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2095</v>
+        <v>0.4646</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1346</v>
+        <v>-0.5403</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2338</v>
+        <v>0.0289</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1004</v>
+        <v>-0.1732</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3342</v>
+        <v>0.2021</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2030,241 +2121,423 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>M. LLUCIA MONSO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5379</v>
+        <v>0.9362</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6913</v>
+        <v>-0.2999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1534</v>
+        <v>1.2361</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9391</v>
+        <v>0.7023</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7089</v>
+        <v>0.5273</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2302</v>
+        <v>0.1751</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7743</v>
+        <v>0.7772</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0755</v>
+        <v>0.7368</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8498</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7133</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6334</v>
+        <v>-0.2095</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0799</v>
+        <v>0.1346</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1322</v>
+        <v>0.2338</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2189</v>
+        <v>-0.1004</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9133</v>
+        <v>0.3342</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.54</v>
+        <v>0.614</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6687</v>
+        <v>0.614</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8712</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8987</v>
+        <v>0.614</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5216</v>
+        <v>0.614</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.377</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7398</v>
+        <v>0.614</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3073</v>
+        <v>0.614</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5675</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1589</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2144</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9445</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3446</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4835</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1389</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-3.3728</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-4.5262</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.1534</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.774</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.9369</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.8371</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.0607</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.3035</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.7133</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.6334</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.0799</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.1322</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.2189</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I. ISERN CASES</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.6687</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.8712</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.8987</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.5216</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.377</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.7398</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.3073</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.1589</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.2144</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.9445</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.3446</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.4835</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.8828</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484358_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>10.3955</v>
       </c>
-      <c r="E23" t="n">
-        <v>5.346899999999999</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E25" t="n">
+        <v>5.3469</v>
+      </c>
+      <c r="F25" t="n">
         <v>5.0486</v>
       </c>
-      <c r="G23" t="n">
-        <v>-0.3239000000000001</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-2.347</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.0234</v>
-      </c>
-      <c r="J23" t="n">
-        <v>9.641400000000001</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="G25" t="n">
+        <v>-0.3239000000000003</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.3471</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.0235</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9.641299999999999</v>
+      </c>
+      <c r="K25" t="n">
         <v>2.890600000000001</v>
       </c>
-      <c r="L23" t="n">
-        <v>6.751</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L25" t="n">
+        <v>6.750999999999999</v>
+      </c>
+      <c r="M25" t="n">
         <v>-9.965299999999999</v>
       </c>
-      <c r="N23" t="n">
-        <v>-5.2379</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="N25" t="n">
+        <v>-5.237900000000001</v>
+      </c>
+      <c r="O25" t="n">
         <v>-4.7275</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>2.9301</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q25" t="n">
         <v>-12.6973</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>15.6273</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>5.4616</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>1.033</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>4.4285</v>
       </c>
-      <c r="V23" t="n">
-        <v>2.3276</v>
-      </c>
-      <c r="W23" t="n">
-        <v>7.369599999999999</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="V25" t="n">
+        <v>2.327600000000001</v>
+      </c>
+      <c r="W25" t="n">
+        <v>7.3696</v>
+      </c>
+      <c r="X25" t="n">
         <v>-5.0421</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
